--- a/04-ai-governance-and-technical-lifecycle/artifacts/A-28_Gate_Approval_and_Signoff_Log.xlsx
+++ b/04-ai-governance-and-technical-lifecycle/artifacts/A-28_Gate_Approval_and_Signoff_Log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Career\Portfolio\Project4\Artifacts V2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Career\Portfolio\Project4\Artifacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B5BD2A-4B0A-499C-A66A-B3577F3E7153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE5B288-D49B-4BBB-819C-74E2D36AED5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -52,9 +52,6 @@
     <t>Purpose</t>
   </si>
   <si>
-    <t>The authoritative record of who approved, blocked, or released each of the eight governance gates, and on what date. This is the artefact that makes gate governance auditable rather than narrative.</t>
-  </si>
-  <si>
     <t>Why this exists separately</t>
   </si>
   <si>
@@ -307,9 +304,6 @@
     <t>NOT REACHED</t>
   </si>
   <si>
-    <t>System is in production. This row exists so the log is complete across all eight gates rather than silently ending at the current gate.</t>
-  </si>
-  <si>
     <t>On decommission</t>
   </si>
   <si>
@@ -560,6 +554,12 @@
   </si>
   <si>
     <t>Control Checks On This Log</t>
+  </si>
+  <si>
+    <t>The authoritative record of who approved, blocked, or released each of the seven decision points (D1–D7), which map to five formal stage gates plus two post-deployment stages (see A-25 §3), and on what date. This is the artefact that makes gate governance auditable rather than narrative.</t>
+  </si>
+  <si>
+    <t>Retirement stage not reached in the worked scenario. This row exists so the log spans all seven decision points rather than silently ending at the current stage.</t>
   </si>
 </sst>
 </file>
@@ -1019,47 +1019,47 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>5</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1089,50 +1089,50 @@
   <sheetData>
     <row r="1" spans="1:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="C4" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="D4" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="E4" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="F4" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="G4" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="H4" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="I4" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="J4" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="17" t="s">
+      <c r="K4" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="17" t="s">
+      <c r="L4" s="17" t="s">
         <v>27</v>
-      </c>
-      <c r="L4" s="17" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1140,37 +1140,37 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="J5" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="K5" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="L5" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1178,37 +1178,37 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H6" s="7" t="s">
+      <c r="I6" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="J6" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="K6" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="L6" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1216,37 +1216,37 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>40</v>
-      </c>
       <c r="D7" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="I7" s="5" t="s">
+      <c r="J7" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="K7" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="L7" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1254,37 +1254,37 @@
         <v>4</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="J8" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="K8" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="L8" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1292,37 +1292,37 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="G9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I9" s="5" t="s">
+      <c r="J9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="J9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="K9" s="5" t="s">
+      <c r="L9" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1330,37 +1330,37 @@
         <v>6</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="5" t="s">
+      <c r="H10" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H10" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="I10" s="5" t="s">
+      <c r="J10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K10" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="J10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="K10" s="5" t="s">
+      <c r="L10" s="5" t="s">
         <v>72</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1368,37 +1368,37 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="5" t="s">
+      <c r="F11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="I11" s="5" t="s">
+      <c r="J11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K11" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="J11" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>78</v>
-      </c>
       <c r="L11" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1406,37 +1406,37 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="D12" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="E12" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="F12" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="F12" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="9" t="s">
+      <c r="H12" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I12" s="9" t="s">
+      <c r="J12" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K12" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="J12" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="K12" s="9" t="s">
+      <c r="L12" s="9" t="s">
         <v>85</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1444,47 +1444,47 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="D13" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="E13" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="L13" s="11" t="s">
         <v>89</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="K13" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="L13" s="11" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B16" s="15">
         <f>COUNTIF(D5:D13,"APPROVED")+COUNTIF(D5:D13,"APPROVED (released)")</f>
@@ -1493,7 +1493,7 @@
     </row>
     <row r="17" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B17" s="15">
         <f>COUNTIF(D5:D13,"BLOCKED")</f>
@@ -1502,7 +1502,7 @@
     </row>
     <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B18" s="15">
         <f>COUNTIF(D5:D13,"SCHEDULED")+COUNTIF(D5:D13,"NOT REACHED")</f>
@@ -1511,7 +1511,7 @@
     </row>
     <row r="19" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B19" s="15">
         <f>COUNTA(D5:D13)</f>
@@ -1540,38 +1540,38 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="17" t="s">
-        <v>18</v>
-      </c>
       <c r="C4" s="17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="F4" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="G4" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="H4" s="17" t="s">
         <v>100</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="103.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1579,25 +1579,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="103.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1605,25 +1605,25 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="103.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1631,25 +1631,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>116</v>
-      </c>
       <c r="H7" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="103.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1657,25 +1657,25 @@
         <v>4</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>120</v>
-      </c>
       <c r="H8" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="103.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1683,25 +1683,25 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>124</v>
-      </c>
       <c r="H9" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="103.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1709,25 +1709,25 @@
         <v>6</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>127</v>
-      </c>
       <c r="H10" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="103.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1735,25 +1735,25 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>131</v>
-      </c>
       <c r="H11" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1777,192 +1777,192 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="18" customFormat="1" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="E4" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="F4" s="17" t="s">
         <v>135</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -1984,116 +1984,116 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="D4" s="17" t="s">
         <v>150</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C5" s="16" t="str">
         <f>IF(COUNTA('GATE-LOG'!B5:B13)=9,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C6" s="16" t="str">
         <f>IF(COUNTIF('GATE-LOG'!H5:H13,"—")&lt;=1,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" s="16" t="str">
         <f>IF(SUMPRODUCT(('GATE-LOG'!F5:F13='GATE-LOG'!G5:G13)*('GATE-LOG'!F5:F13&lt;&gt;"—"))=0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C8" s="16" t="str">
         <f>IF(COUNTIF('GATE-LOG'!D5:D13,"BLOCKED")&gt;0,"PASS","REVIEW")</f>
         <v>PASS</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C9" s="16" t="str">
         <f>IF(COUNTIFS('GATE-LOG'!D5:D13,"BLOCKED",'GATE-LOG'!J5:J13,"—")=0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C10" s="16" t="str">
         <f>IF(COUNTIF('GATE-LOG'!L5:L13,"")=0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
